--- a/sources/ganryu_step5b.xlsx
+++ b/sources/ganryu_step5b.xlsx
@@ -722,6 +722,11 @@
           <t>Opponent can tech roll after the throw.</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>2a7ac50b-41fc-4e71-b0c5-5b89e00a22db</t>
@@ -769,6 +774,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>772009bb-1ba2-4bed-a93b-b143fc09bbac</t>
@@ -816,6 +826,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>3a4f81fa-8568-40b0-912f-e46ef9153678</t>
@@ -858,6 +873,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>5bc9fb38-18e7-401d-903c-7e16457c54ea</t>
@@ -903,6 +923,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>06da1e67-d557-429d-bbe8-0414aa87e38a</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">

--- a/sources/ganryu_step5b.xlsx
+++ b/sources/ganryu_step5b.xlsx
@@ -2516,7 +2516,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4445,6 +4445,11 @@
           <t>–– u</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>–– Splits Side Step</t>
@@ -4809,6 +4814,11 @@
           <t>–– u</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>–– Splits Side Step</t>
@@ -5099,6 +5109,11 @@
       <c r="A89" t="inlineStr">
         <is>
           <t>–– u</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>d</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
